--- a/sources/paul_step3.xlsx
+++ b/sources/paul_step3.xlsx
@@ -769,6 +769,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1bddff50-c0df-40c7-9efa-29b264583940</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>1bddff50-c0df-40c7-9efa-29b264583940</t>
@@ -801,6 +806,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>39dff7b9-ce44-4948-ad1f-b1ef695ca9a3</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>39dff7b9-ce44-4948-ad1f-b1ef695ca9a3</t>
@@ -838,6 +848,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>701e73a5-cb4f-442c-95a1-4a3d33f87d73</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>701e73a5-cb4f-442c-95a1-4a3d33f87d73</t>
@@ -875,6 +890,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0837c7ed-0764-4f99-a630-8ac829f5cd48</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>0837c7ed-0764-4f99-a630-8ac829f5cd48</t>
@@ -912,6 +932,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>8f4adaf4-8d96-4db4-9e5d-c30c5a7019be</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
           <t>8f4adaf4-8d96-4db4-9e5d-c30c5a7019be</t>
@@ -949,6 +974,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>9ceaa1aa-aa76-418f-a422-c4dcb6b6e146</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>9ceaa1aa-aa76-418f-a422-c4dcb6b6e146</t>
@@ -986,6 +1016,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>b7497a64-e28b-4906-90d2-9ce8f800b5db</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>b7497a64-e28b-4906-90d2-9ce8f800b5db</t>
@@ -1028,6 +1063,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>298a11b7-cb2d-4207-89d4-785146ac1d79</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>298a11b7-cb2d-4207-89d4-785146ac1d79</t>
@@ -1065,6 +1105,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>f4807f21-048f-4fcc-be89-b4ed5bad669d</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>f4807f21-048f-4fcc-be89-b4ed5bad669d</t>
@@ -1100,6 +1145,11 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>714cac8f-98de-4f0c-bfac-510c28ebaccd</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -4698,6 +4748,11 @@
           <t>hhmmlmhmLm</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>8b2ab344-e968-4445-b403-e548e2f0db2d</t>
+        </is>
+      </c>
       <c r="O92" t="inlineStr">
         <is>
           <t>8b2ab344-e968-4445-b403-e548e2f0db2d</t>
@@ -4725,6 +4780,11 @@
           <t>hhmhmhhlmm</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>9c058e2e-80b5-4da3-b171-a802077dec24</t>
+        </is>
+      </c>
       <c r="O93" t="inlineStr">
         <is>
           <t>9c058e2e-80b5-4da3-b171-a802077dec24</t>
@@ -4750,6 +4810,11 @@
       <c r="I94" t="inlineStr">
         <is>
           <t>hhmmm</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>e1a2f47f-32a9-46a1-bc65-d50cded77733</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
